--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ\Data Files\Backoffce\IndexacaoFG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68569B4E-A6B3-4BED-AC28-653CA35B12E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A11FAB6-2DF0-4D8E-8716-AD26D62D1E39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="14">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,27 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 18.08.2025</t>
+  </si>
+  <si>
+    <t>133855392</t>
+  </si>
+  <si>
+    <t>971</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 18.08.2025</t>
+  </si>
+  <si>
+    <t>133930070</t>
+  </si>
+  <si>
+    <t>133756889</t>
+  </si>
+  <si>
+    <t>133986492</t>
   </si>
 </sst>
 </file>
@@ -444,7 +465,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -475,12 +496,70 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="E3" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A11FAB6-2DF0-4D8E-8716-AD26D62D1E39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B569BCB-1421-4C52-80D0-41DFF931C8C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="16">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,25 +51,31 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>Recusa Sicoob 18.08.2025</t>
-  </si>
-  <si>
-    <t>133855392</t>
-  </si>
-  <si>
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa SICOOB 18.08.2025</t>
-  </si>
-  <si>
-    <t>133930070</t>
-  </si>
-  <si>
-    <t>133756889</t>
-  </si>
-  <si>
-    <t>133986492</t>
+    <t>Recusa Sicoob 19.08.2025</t>
+  </si>
+  <si>
+    <t>133870282</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 19.08.2025</t>
+  </si>
+  <si>
+    <t>133804777</t>
+  </si>
+  <si>
+    <t>133926737</t>
+  </si>
+  <si>
+    <t>133950374</t>
+  </si>
+  <si>
+    <t>133874778</t>
+  </si>
+  <si>
+    <t>129399774</t>
   </si>
 </sst>
 </file>
@@ -465,7 +471,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -497,16 +503,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -517,13 +523,13 @@
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -534,13 +540,13 @@
         <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -551,15 +557,49 @@
         <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="C6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B569BCB-1421-4C52-80D0-41DFF931C8C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E488C913-4413-467E-9E1E-048EA6E2368B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -54,28 +54,28 @@
     <t>971</t>
   </si>
   <si>
-    <t>Recusa Sicoob 19.08.2025</t>
-  </si>
-  <si>
-    <t>133870282</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 19.08.2025</t>
-  </si>
-  <si>
-    <t>133804777</t>
-  </si>
-  <si>
-    <t>133926737</t>
-  </si>
-  <si>
-    <t>133950374</t>
-  </si>
-  <si>
-    <t>133874778</t>
-  </si>
-  <si>
-    <t>129399774</t>
+    <t>Recusa Sicoob 20.08.2025</t>
+  </si>
+  <si>
+    <t>133885726</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 20.08.2025</t>
+  </si>
+  <si>
+    <t>133940243</t>
+  </si>
+  <si>
+    <t>133942988</t>
+  </si>
+  <si>
+    <t>133895460</t>
+  </si>
+  <si>
+    <t>888207201</t>
+  </si>
+  <si>
+    <t>134037858</t>
   </si>
 </sst>
 </file>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E488C913-4413-467E-9E1E-048EA6E2368B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C76A9A16-B8E5-4CCF-B61C-6E1815242794}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="17">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,28 +54,31 @@
     <t>971</t>
   </si>
   <si>
-    <t>Recusa Sicoob 20.08.2025</t>
-  </si>
-  <si>
-    <t>133885726</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 20.08.2025</t>
-  </si>
-  <si>
-    <t>133940243</t>
-  </si>
-  <si>
-    <t>133942988</t>
-  </si>
-  <si>
-    <t>133895460</t>
-  </si>
-  <si>
-    <t>888207201</t>
-  </si>
-  <si>
-    <t>134037858</t>
+    <t>Recusa Sicoob 21.08.2025</t>
+  </si>
+  <si>
+    <t>133959670</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 21.08.2025</t>
+  </si>
+  <si>
+    <t>133951695</t>
+  </si>
+  <si>
+    <t>133850849</t>
+  </si>
+  <si>
+    <t>133922444</t>
+  </si>
+  <si>
+    <t>133893564</t>
+  </si>
+  <si>
+    <t>133964312</t>
+  </si>
+  <si>
+    <t>133904254</t>
   </si>
 </sst>
 </file>
@@ -471,7 +474,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -603,6 +606,23 @@
         <v>6</v>
       </c>
     </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C76A9A16-B8E5-4CCF-B61C-6E1815242794}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0E44104-BBB0-4F70-87AF-7043608F3A06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -54,31 +54,31 @@
     <t>971</t>
   </si>
   <si>
-    <t>Recusa Sicoob 21.08.2025</t>
-  </si>
-  <si>
-    <t>133959670</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 21.08.2025</t>
-  </si>
-  <si>
-    <t>133951695</t>
-  </si>
-  <si>
-    <t>133850849</t>
-  </si>
-  <si>
-    <t>133922444</t>
-  </si>
-  <si>
-    <t>133893564</t>
-  </si>
-  <si>
-    <t>133964312</t>
-  </si>
-  <si>
-    <t>133904254</t>
+    <t>130332735</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 22.08.2025</t>
+  </si>
+  <si>
+    <t>129880995</t>
+  </si>
+  <si>
+    <t>133982526</t>
+  </si>
+  <si>
+    <t>130999634</t>
+  </si>
+  <si>
+    <t>133930922</t>
+  </si>
+  <si>
+    <t>133937928</t>
+  </si>
+  <si>
+    <t>133940561</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 22.08.2025</t>
   </si>
 </sst>
 </file>
@@ -506,16 +506,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -523,16 +523,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -540,16 +540,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -557,16 +557,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -574,16 +574,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -591,16 +591,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -608,16 +608,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0E44104-BBB0-4F70-87AF-7043608F3A06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{026CBF77-6751-4E67-A528-1EC97F07D0BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="14">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,31 +54,22 @@
     <t>971</t>
   </si>
   <si>
-    <t>130332735</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 22.08.2025</t>
-  </si>
-  <si>
-    <t>129880995</t>
-  </si>
-  <si>
-    <t>133982526</t>
-  </si>
-  <si>
-    <t>130999634</t>
-  </si>
-  <si>
-    <t>133930922</t>
-  </si>
-  <si>
-    <t>133937928</t>
-  </si>
-  <si>
-    <t>133940561</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 22.08.2025</t>
+    <t>Indexacao FG Recusa Sicoob 25.08.2025</t>
+  </si>
+  <si>
+    <t>133964156</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 25.08.2025</t>
+  </si>
+  <si>
+    <t>134031557</t>
+  </si>
+  <si>
+    <t>133227088</t>
+  </si>
+  <si>
+    <t>131258251</t>
   </si>
 </sst>
 </file>
@@ -474,7 +465,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -506,16 +497,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -523,16 +514,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -540,16 +531,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -557,69 +548,18 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{026CBF77-6751-4E67-A528-1EC97F07D0BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A0E64E6-8CE1-44F0-BD33-E2586E144F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1515" yWindow="1515" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="15">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,22 +54,25 @@
     <t>971</t>
   </si>
   <si>
-    <t>Indexacao FG Recusa Sicoob 25.08.2025</t>
-  </si>
-  <si>
-    <t>133964156</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 25.08.2025</t>
-  </si>
-  <si>
-    <t>134031557</t>
-  </si>
-  <si>
-    <t>133227088</t>
-  </si>
-  <si>
-    <t>131258251</t>
+    <t>Recusa Sicoob 26.08.2025</t>
+  </si>
+  <si>
+    <t>130493804</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 26.08.2025</t>
+  </si>
+  <si>
+    <t>134110043</t>
+  </si>
+  <si>
+    <t>133986612</t>
+  </si>
+  <si>
+    <t>133985210</t>
+  </si>
+  <si>
+    <t>133906147</t>
   </si>
 </sst>
 </file>
@@ -465,7 +468,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -563,6 +566,23 @@
         <v>6</v>
       </c>
     </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A0E64E6-8CE1-44F0-BD33-E2586E144F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D27CA6EC-18B6-4430-B79D-7F8CDB69299D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1515" yWindow="1515" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,25 +54,19 @@
     <t>971</t>
   </si>
   <si>
-    <t>Recusa Sicoob 26.08.2025</t>
-  </si>
-  <si>
-    <t>130493804</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 26.08.2025</t>
-  </si>
-  <si>
-    <t>134110043</t>
-  </si>
-  <si>
-    <t>133986612</t>
-  </si>
-  <si>
-    <t>133985210</t>
-  </si>
-  <si>
-    <t>133906147</t>
+    <t>Recusa Sicoob 27.08.2025</t>
+  </si>
+  <si>
+    <t>134016433</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 27.08.2025</t>
+  </si>
+  <si>
+    <t>134070278</t>
+  </si>
+  <si>
+    <t>134012541</t>
   </si>
 </sst>
 </file>
@@ -468,7 +462,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -549,40 +543,6 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D27CA6EC-18B6-4430-B79D-7F8CDB69299D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44613486-596E-4B51-B886-7D56B223C030}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="17">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,19 +54,31 @@
     <t>971</t>
   </si>
   <si>
-    <t>Recusa Sicoob 27.08.2025</t>
-  </si>
-  <si>
-    <t>134016433</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 27.08.2025</t>
-  </si>
-  <si>
-    <t>134070278</t>
-  </si>
-  <si>
-    <t>134012541</t>
+    <t>Recusa Sicoob 28.08.2025</t>
+  </si>
+  <si>
+    <t>134029637</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 28.08.2025</t>
+  </si>
+  <si>
+    <t>134074888</t>
+  </si>
+  <si>
+    <t>134141524</t>
+  </si>
+  <si>
+    <t>134081814</t>
+  </si>
+  <si>
+    <t>134174030</t>
+  </si>
+  <si>
+    <t>132593972</t>
+  </si>
+  <si>
+    <t>133484827</t>
   </si>
 </sst>
 </file>
@@ -462,7 +474,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -543,6 +555,74 @@
         <v>6</v>
       </c>
     </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44613486-596E-4B51-B886-7D56B223C030}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D23BA75D-BCB5-4E19-A372-29081DE4AED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="16">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,31 +54,28 @@
     <t>971</t>
   </si>
   <si>
-    <t>Recusa Sicoob 28.08.2025</t>
-  </si>
-  <si>
-    <t>134029637</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 28.08.2025</t>
-  </si>
-  <si>
-    <t>134074888</t>
-  </si>
-  <si>
-    <t>134141524</t>
-  </si>
-  <si>
-    <t>134081814</t>
-  </si>
-  <si>
-    <t>134174030</t>
-  </si>
-  <si>
-    <t>132593972</t>
-  </si>
-  <si>
-    <t>133484827</t>
+    <t>134068263</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 29.08.2025</t>
+  </si>
+  <si>
+    <t>131054141</t>
+  </si>
+  <si>
+    <t>134182209</t>
+  </si>
+  <si>
+    <t>131108755</t>
+  </si>
+  <si>
+    <t>130395030</t>
+  </si>
+  <si>
+    <t>134198247</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 29.08.2025</t>
   </si>
 </sst>
 </file>
@@ -474,7 +471,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -506,16 +503,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -523,16 +520,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -540,16 +537,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -557,16 +554,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -574,16 +571,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -591,35 +588,18 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D23BA75D-BCB5-4E19-A372-29081DE4AED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBB22CF6-735F-47A9-A6D8-16E2108E3B00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="15">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,28 +54,25 @@
     <t>971</t>
   </si>
   <si>
-    <t>134068263</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 29.08.2025</t>
-  </si>
-  <si>
-    <t>131054141</t>
-  </si>
-  <si>
-    <t>134182209</t>
-  </si>
-  <si>
-    <t>131108755</t>
-  </si>
-  <si>
-    <t>130395030</t>
-  </si>
-  <si>
-    <t>134198247</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 29.08.2025</t>
+    <t>Recusa Sicoob 01.09.2025</t>
+  </si>
+  <si>
+    <t>134108954</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 01.09.2025</t>
+  </si>
+  <si>
+    <t>134100372</t>
+  </si>
+  <si>
+    <t>134141435</t>
+  </si>
+  <si>
+    <t>134180534</t>
+  </si>
+  <si>
+    <t>134080184</t>
   </si>
 </sst>
 </file>
@@ -503,16 +500,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -520,16 +517,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -537,16 +534,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -554,16 +551,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -571,38 +568,22 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
+    <row r="7" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBB22CF6-735F-47A9-A6D8-16E2108E3B00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{746A167D-5F52-4602-A9C2-F5791C8EB234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="20">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,25 +54,40 @@
     <t>971</t>
   </si>
   <si>
-    <t>Recusa Sicoob 01.09.2025</t>
-  </si>
-  <si>
-    <t>134108954</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 01.09.2025</t>
-  </si>
-  <si>
-    <t>134100372</t>
-  </si>
-  <si>
-    <t>134141435</t>
-  </si>
-  <si>
-    <t>134180534</t>
-  </si>
-  <si>
-    <t>134080184</t>
+    <t>Recusa Sicoob 02.09.2025</t>
+  </si>
+  <si>
+    <t>130493804</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 02.09.2025</t>
+  </si>
+  <si>
+    <t>134173702</t>
+  </si>
+  <si>
+    <t>134217010</t>
+  </si>
+  <si>
+    <t>134129658</t>
+  </si>
+  <si>
+    <t>134239558</t>
+  </si>
+  <si>
+    <t>134240526</t>
+  </si>
+  <si>
+    <t>134100896</t>
+  </si>
+  <si>
+    <t>134152295</t>
+  </si>
+  <si>
+    <t>134239600</t>
+  </si>
+  <si>
+    <t>134249874</t>
   </si>
 </sst>
 </file>
@@ -468,7 +483,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -583,7 +598,91 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{746A167D-5F52-4602-A9C2-F5791C8EB234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC6EF90D-E6A3-4B1D-A674-1F401EA6F992}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="16">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,40 +54,28 @@
     <t>971</t>
   </si>
   <si>
-    <t>Recusa Sicoob 02.09.2025</t>
-  </si>
-  <si>
-    <t>130493804</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 02.09.2025</t>
-  </si>
-  <si>
-    <t>134173702</t>
-  </si>
-  <si>
-    <t>134217010</t>
-  </si>
-  <si>
-    <t>134129658</t>
-  </si>
-  <si>
-    <t>134239558</t>
-  </si>
-  <si>
-    <t>134240526</t>
-  </si>
-  <si>
-    <t>134100896</t>
-  </si>
-  <si>
-    <t>134152295</t>
-  </si>
-  <si>
-    <t>134239600</t>
-  </si>
-  <si>
-    <t>134249874</t>
+    <t>Recusa Sicoob 04.09.2025</t>
+  </si>
+  <si>
+    <t>134129786</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 04.09.2025</t>
+  </si>
+  <si>
+    <t>134073927</t>
+  </si>
+  <si>
+    <t>131572305</t>
+  </si>
+  <si>
+    <t>134180623</t>
+  </si>
+  <si>
+    <t>134118231</t>
+  </si>
+  <si>
+    <t>134144028</t>
   </si>
 </sst>
 </file>
@@ -483,7 +471,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -615,74 +603,6 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC6EF90D-E6A3-4B1D-A674-1F401EA6F992}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A292F71D-3FE8-4E3A-9C73-93506D9E3F12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,28 +54,13 @@
     <t>971</t>
   </si>
   <si>
-    <t>Recusa Sicoob 04.09.2025</t>
-  </si>
-  <si>
-    <t>134129786</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 04.09.2025</t>
-  </si>
-  <si>
-    <t>134073927</t>
-  </si>
-  <si>
-    <t>131572305</t>
-  </si>
-  <si>
-    <t>134180623</t>
-  </si>
-  <si>
-    <t>134118231</t>
-  </si>
-  <si>
-    <t>134144028</t>
+    <t>134162609</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 05.09.2025</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 05.09.2025</t>
   </si>
 </sst>
 </file>
@@ -503,106 +488,22 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
+    <row r="7" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A292F71D-3FE8-4E3A-9C73-93506D9E3F12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9390CFA4-3B03-4380-A3EC-A45F82196E87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9390CFA4-3B03-4380-A3EC-A45F82196E87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96254EF9-9FD1-421E-BFA3-02869894237A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="21">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,13 +54,43 @@
     <t>971</t>
   </si>
   <si>
-    <t>134162609</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 05.09.2025</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 05.09.2025</t>
+    <t>Recusa Sicoob 08.09.2025</t>
+  </si>
+  <si>
+    <t>134202140</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 08.09.2025</t>
+  </si>
+  <si>
+    <t>134207088</t>
+  </si>
+  <si>
+    <t>134310725</t>
+  </si>
+  <si>
+    <t>134321683</t>
+  </si>
+  <si>
+    <t>134336610</t>
+  </si>
+  <si>
+    <t>134249769</t>
+  </si>
+  <si>
+    <t>134221806</t>
+  </si>
+  <si>
+    <t>134344839</t>
+  </si>
+  <si>
+    <t>134206240</t>
+  </si>
+  <si>
+    <t>134192880</t>
+  </si>
+  <si>
+    <t>134195275</t>
   </si>
 </sst>
 </file>
@@ -456,7 +486,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -488,22 +518,191 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96254EF9-9FD1-421E-BFA3-02869894237A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF1B039B-3F79-4712-9BA8-FA70CAD161E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="18">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,43 +54,34 @@
     <t>971</t>
   </si>
   <si>
-    <t>Recusa Sicoob 08.09.2025</t>
-  </si>
-  <si>
-    <t>134202140</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 08.09.2025</t>
-  </si>
-  <si>
-    <t>134207088</t>
-  </si>
-  <si>
-    <t>134310725</t>
-  </si>
-  <si>
-    <t>134321683</t>
-  </si>
-  <si>
-    <t>134336610</t>
-  </si>
-  <si>
-    <t>134249769</t>
-  </si>
-  <si>
-    <t>134221806</t>
-  </si>
-  <si>
-    <t>134344839</t>
-  </si>
-  <si>
-    <t>134206240</t>
-  </si>
-  <si>
-    <t>134192880</t>
-  </si>
-  <si>
-    <t>134195275</t>
+    <t>134228179</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 09.09.2025</t>
+  </si>
+  <si>
+    <t>134293353</t>
+  </si>
+  <si>
+    <t>134335227</t>
+  </si>
+  <si>
+    <t>130395030</t>
+  </si>
+  <si>
+    <t>134353932</t>
+  </si>
+  <si>
+    <t>134363419</t>
+  </si>
+  <si>
+    <t>134368323</t>
+  </si>
+  <si>
+    <t>134164361</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 09.09.2025</t>
   </si>
 </sst>
 </file>
@@ -486,7 +477,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -518,16 +509,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -535,16 +526,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -552,16 +543,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -569,16 +560,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -586,16 +577,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -603,16 +594,16 @@
     </row>
     <row r="7" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -620,16 +611,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -637,69 +628,18 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF1B039B-3F79-4712-9BA8-FA70CAD161E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A654039-F1EA-4BB2-904A-9B7E1C89975A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="26115" yWindow="2220" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="16">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,34 +54,28 @@
     <t>971</t>
   </si>
   <si>
-    <t>134228179</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 09.09.2025</t>
-  </si>
-  <si>
-    <t>134293353</t>
-  </si>
-  <si>
-    <t>134335227</t>
-  </si>
-  <si>
-    <t>130395030</t>
-  </si>
-  <si>
-    <t>134353932</t>
-  </si>
-  <si>
-    <t>134363419</t>
-  </si>
-  <si>
-    <t>134368323</t>
-  </si>
-  <si>
     <t>134164361</t>
   </si>
   <si>
-    <t>Recusa Sicoob 09.09.2025</t>
+    <t>134269174</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 10.09.2025</t>
+  </si>
+  <si>
+    <t>134341723</t>
+  </si>
+  <si>
+    <t>134375637</t>
+  </si>
+  <si>
+    <t>134376356</t>
+  </si>
+  <si>
+    <t>134389562</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 10.09.2025</t>
   </si>
 </sst>
 </file>
@@ -477,7 +471,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -509,16 +503,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -526,16 +520,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -543,16 +537,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -566,10 +560,10 @@
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -583,10 +577,10 @@
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -600,46 +594,12 @@
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A654039-F1EA-4BB2-904A-9B7E1C89975A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{070E983B-D8D1-402B-B0BE-D882EC7E8810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="26115" yWindow="2220" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="18">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,28 +54,34 @@
     <t>971</t>
   </si>
   <si>
-    <t>134164361</t>
-  </si>
-  <si>
-    <t>134269174</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 10.09.2025</t>
-  </si>
-  <si>
-    <t>134341723</t>
-  </si>
-  <si>
-    <t>134375637</t>
-  </si>
-  <si>
-    <t>134376356</t>
-  </si>
-  <si>
-    <t>134389562</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 10.09.2025</t>
+    <t>134317754</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 11.09.2025</t>
+  </si>
+  <si>
+    <t>134385749</t>
+  </si>
+  <si>
+    <t>134293522</t>
+  </si>
+  <si>
+    <t>134401832</t>
+  </si>
+  <si>
+    <t>134402230</t>
+  </si>
+  <si>
+    <t>134298398</t>
+  </si>
+  <si>
+    <t>134270681</t>
+  </si>
+  <si>
+    <t>134273448</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 11.09.2025</t>
   </si>
 </sst>
 </file>
@@ -471,7 +477,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -503,16 +509,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -520,16 +526,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -537,16 +543,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -560,10 +566,10 @@
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -577,10 +583,10 @@
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -594,12 +600,46 @@
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{070E983B-D8D1-402B-B0BE-D882EC7E8810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64D9BADD-6387-420C-A227-11BD7B66A4D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="22">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,34 +54,46 @@
     <t>971</t>
   </si>
   <si>
-    <t>134317754</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 11.09.2025</t>
-  </si>
-  <si>
-    <t>134385749</t>
-  </si>
-  <si>
-    <t>134293522</t>
-  </si>
-  <si>
-    <t>134401832</t>
-  </si>
-  <si>
-    <t>134402230</t>
-  </si>
-  <si>
-    <t>134298398</t>
-  </si>
-  <si>
-    <t>134270681</t>
-  </si>
-  <si>
-    <t>134273448</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 11.09.2025</t>
+    <t>134350065</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 12.09.2025</t>
+  </si>
+  <si>
+    <t>134357459</t>
+  </si>
+  <si>
+    <t>134399472</t>
+  </si>
+  <si>
+    <t>134228037</t>
+  </si>
+  <si>
+    <t>134284477</t>
+  </si>
+  <si>
+    <t>130894990</t>
+  </si>
+  <si>
+    <t>134345543</t>
+  </si>
+  <si>
+    <t>134341355</t>
+  </si>
+  <si>
+    <t>134432999</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 12.09.2025</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 13.09.2025</t>
+  </si>
+  <si>
+    <t>134240856</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 13.09.2025</t>
   </si>
 </sst>
 </file>
@@ -477,7 +489,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -518,7 +530,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -535,7 +547,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -552,7 +564,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -569,7 +581,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -586,7 +598,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -603,7 +615,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -620,7 +632,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -637,9 +649,43 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64D9BADD-6387-420C-A227-11BD7B66A4D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9AE402C-3D80-4BB6-9B6C-D9052D6B6360}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="15">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,46 +54,25 @@
     <t>971</t>
   </si>
   <si>
-    <t>134350065</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 12.09.2025</t>
-  </si>
-  <si>
-    <t>134357459</t>
-  </si>
-  <si>
-    <t>134399472</t>
-  </si>
-  <si>
-    <t>134228037</t>
-  </si>
-  <si>
-    <t>134284477</t>
-  </si>
-  <si>
-    <t>130894990</t>
-  </si>
-  <si>
-    <t>134345543</t>
-  </si>
-  <si>
-    <t>134341355</t>
-  </si>
-  <si>
-    <t>134432999</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 12.09.2025</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 13.09.2025</t>
-  </si>
-  <si>
-    <t>134240856</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 13.09.2025</t>
+    <t>134343227</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 15.09.2025</t>
+  </si>
+  <si>
+    <t>134397190</t>
+  </si>
+  <si>
+    <t>133624407</t>
+  </si>
+  <si>
+    <t>133780926</t>
+  </si>
+  <si>
+    <t>132831287</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 15.09.2025</t>
   </si>
 </sst>
 </file>
@@ -489,7 +468,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -530,7 +509,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -547,7 +526,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -564,7 +543,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -581,7 +560,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -598,97 +577,13 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
+    <row r="7" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9AE402C-3D80-4BB6-9B6C-D9052D6B6360}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2249DD8-EC31-4999-94FB-BBE9D71C3C1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="18">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,25 +54,34 @@
     <t>971</t>
   </si>
   <si>
-    <t>134343227</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 15.09.2025</t>
-  </si>
-  <si>
-    <t>134397190</t>
-  </si>
-  <si>
-    <t>133624407</t>
-  </si>
-  <si>
-    <t>133780926</t>
-  </si>
-  <si>
-    <t>132831287</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 15.09.2025</t>
+    <t>Recusa Sicoob 16.09.2025</t>
+  </si>
+  <si>
+    <t>134416591</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 16.09.2025</t>
+  </si>
+  <si>
+    <t>134429416</t>
+  </si>
+  <si>
+    <t>134474167</t>
+  </si>
+  <si>
+    <t>134468275</t>
+  </si>
+  <si>
+    <t>131095074</t>
+  </si>
+  <si>
+    <t>134466304</t>
+  </si>
+  <si>
+    <t>134343728</t>
+  </si>
+  <si>
+    <t>134345481</t>
   </si>
 </sst>
 </file>
@@ -468,7 +477,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -500,16 +509,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -517,16 +526,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -534,16 +543,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -551,16 +560,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -568,22 +577,72 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2249DD8-EC31-4999-94FB-BBE9D71C3C1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF2B0695-1E83-4852-9E19-7D8B8B8C7992}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="20">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,34 +54,40 @@
     <t>971</t>
   </si>
   <si>
-    <t>Recusa Sicoob 16.09.2025</t>
-  </si>
-  <si>
-    <t>134416591</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 16.09.2025</t>
-  </si>
-  <si>
-    <t>134429416</t>
-  </si>
-  <si>
-    <t>134474167</t>
-  </si>
-  <si>
-    <t>134468275</t>
-  </si>
-  <si>
-    <t>131095074</t>
-  </si>
-  <si>
-    <t>134466304</t>
-  </si>
-  <si>
-    <t>134343728</t>
-  </si>
-  <si>
-    <t>134345481</t>
+    <t>Recusa Sicoob 17.09.2025</t>
+  </si>
+  <si>
+    <t>134357842</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 17.09.2025</t>
+  </si>
+  <si>
+    <t>134364012</t>
+  </si>
+  <si>
+    <t>134367104</t>
+  </si>
+  <si>
+    <t>134386143</t>
+  </si>
+  <si>
+    <t>134410417</t>
+  </si>
+  <si>
+    <t>134236594</t>
+  </si>
+  <si>
+    <t>134395547</t>
+  </si>
+  <si>
+    <t>134376568</t>
+  </si>
+  <si>
+    <t>134496459</t>
+  </si>
+  <si>
+    <t>134368659</t>
   </si>
 </sst>
 </file>
@@ -477,7 +483,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -643,6 +649,40 @@
         <v>6</v>
       </c>
     </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF2B0695-1E83-4852-9E19-7D8B8B8C7992}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96EC9A26-4EF0-4DCD-89E9-2B894821C44E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="24">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,40 +54,52 @@
     <t>971</t>
   </si>
   <si>
-    <t>Recusa Sicoob 17.09.2025</t>
-  </si>
-  <si>
-    <t>134357842</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 17.09.2025</t>
-  </si>
-  <si>
-    <t>134364012</t>
-  </si>
-  <si>
-    <t>134367104</t>
-  </si>
-  <si>
-    <t>134386143</t>
-  </si>
-  <si>
-    <t>134410417</t>
-  </si>
-  <si>
-    <t>134236594</t>
-  </si>
-  <si>
-    <t>134395547</t>
-  </si>
-  <si>
-    <t>134376568</t>
-  </si>
-  <si>
-    <t>134496459</t>
-  </si>
-  <si>
-    <t>134368659</t>
+    <t>Recusa Sicoob 18.09.2025</t>
+  </si>
+  <si>
+    <t>130482292</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 18.09.2025</t>
+  </si>
+  <si>
+    <t>134377528</t>
+  </si>
+  <si>
+    <t>134407249</t>
+  </si>
+  <si>
+    <t>134419264</t>
+  </si>
+  <si>
+    <t>134421640</t>
+  </si>
+  <si>
+    <t>134474678</t>
+  </si>
+  <si>
+    <t>134500711</t>
+  </si>
+  <si>
+    <t>134405087</t>
+  </si>
+  <si>
+    <t>134496328</t>
+  </si>
+  <si>
+    <t>134309176</t>
+  </si>
+  <si>
+    <t>134433118</t>
+  </si>
+  <si>
+    <t>134435634</t>
+  </si>
+  <si>
+    <t>134374304</t>
+  </si>
+  <si>
+    <t>134379890</t>
   </si>
 </sst>
 </file>
@@ -483,7 +495,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -680,6 +692,74 @@
         <v>8</v>
       </c>
       <c r="E11" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96EC9A26-4EF0-4DCD-89E9-2B894821C44E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF729F10-6EEF-4E13-B1E4-0501C28CB385}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="23">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,52 +54,49 @@
     <t>971</t>
   </si>
   <si>
-    <t>Recusa Sicoob 18.09.2025</t>
-  </si>
-  <si>
-    <t>130482292</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 18.09.2025</t>
-  </si>
-  <si>
-    <t>134377528</t>
-  </si>
-  <si>
-    <t>134407249</t>
-  </si>
-  <si>
-    <t>134419264</t>
-  </si>
-  <si>
-    <t>134421640</t>
-  </si>
-  <si>
-    <t>134474678</t>
-  </si>
-  <si>
-    <t>134500711</t>
-  </si>
-  <si>
-    <t>134405087</t>
-  </si>
-  <si>
-    <t>134496328</t>
-  </si>
-  <si>
-    <t>134309176</t>
-  </si>
-  <si>
-    <t>134433118</t>
-  </si>
-  <si>
-    <t>134435634</t>
-  </si>
-  <si>
-    <t>134374304</t>
-  </si>
-  <si>
-    <t>134379890</t>
+    <t>130332735</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 19.09.2025</t>
+  </si>
+  <si>
+    <t>134416309</t>
+  </si>
+  <si>
+    <t>134480187</t>
+  </si>
+  <si>
+    <t>134477524</t>
+  </si>
+  <si>
+    <t>133872183</t>
+  </si>
+  <si>
+    <t>134400882</t>
+  </si>
+  <si>
+    <t>134430093</t>
+  </si>
+  <si>
+    <t>134393725</t>
+  </si>
+  <si>
+    <t>134401386</t>
+  </si>
+  <si>
+    <t>134410891</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 19.09.2025</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 20.09.2025</t>
+  </si>
+  <si>
+    <t>134345879</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 20.09.2025</t>
   </si>
 </sst>
 </file>
@@ -495,7 +492,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -527,16 +524,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -544,16 +541,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -561,16 +558,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -578,16 +575,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -595,16 +592,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -612,16 +609,16 @@
     </row>
     <row r="7" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -629,16 +626,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -646,16 +643,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -663,16 +660,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -680,16 +677,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -697,69 +694,18 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="E12" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E15" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF729F10-6EEF-4E13-B1E4-0501C28CB385}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13CEF33A-A9A6-4FC9-93BA-BFF65A2E9BAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="17">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,49 +54,31 @@
     <t>971</t>
   </si>
   <si>
-    <t>130332735</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 19.09.2025</t>
-  </si>
-  <si>
-    <t>134416309</t>
-  </si>
-  <si>
-    <t>134480187</t>
-  </si>
-  <si>
-    <t>134477524</t>
-  </si>
-  <si>
-    <t>133872183</t>
-  </si>
-  <si>
-    <t>134400882</t>
-  </si>
-  <si>
-    <t>134430093</t>
-  </si>
-  <si>
-    <t>134393725</t>
-  </si>
-  <si>
-    <t>134401386</t>
-  </si>
-  <si>
-    <t>134410891</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 19.09.2025</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 20.09.2025</t>
-  </si>
-  <si>
-    <t>134345879</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 20.09.2025</t>
+    <t>Recusa Sicoob 22.09.2025</t>
+  </si>
+  <si>
+    <t>134436225</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 22.09.2025</t>
+  </si>
+  <si>
+    <t>134473522</t>
+  </si>
+  <si>
+    <t>130894990</t>
+  </si>
+  <si>
+    <t>134573102</t>
+  </si>
+  <si>
+    <t>134425668</t>
+  </si>
+  <si>
+    <t>134577773</t>
+  </si>
+  <si>
+    <t>134578754</t>
   </si>
 </sst>
 </file>
@@ -492,7 +474,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -524,16 +506,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -541,16 +523,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -558,16 +540,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -575,16 +557,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -592,16 +574,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -609,16 +591,16 @@
     </row>
     <row r="7" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -626,86 +608,18 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E12" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13CEF33A-A9A6-4FC9-93BA-BFF65A2E9BAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3108F884-8791-439E-89C2-323F29A63FC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="19">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,31 +54,37 @@
     <t>971</t>
   </si>
   <si>
-    <t>Recusa Sicoob 22.09.2025</t>
-  </si>
-  <si>
-    <t>134436225</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 22.09.2025</t>
-  </si>
-  <si>
-    <t>134473522</t>
-  </si>
-  <si>
-    <t>130894990</t>
-  </si>
-  <si>
-    <t>134573102</t>
-  </si>
-  <si>
-    <t>134425668</t>
-  </si>
-  <si>
-    <t>134577773</t>
-  </si>
-  <si>
-    <t>134578754</t>
+    <t>Recusa Sicoob 23.09.2025</t>
+  </si>
+  <si>
+    <t>134454849</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 23.09.2025</t>
+  </si>
+  <si>
+    <t>134495213</t>
+  </si>
+  <si>
+    <t>134563149</t>
+  </si>
+  <si>
+    <t>130906283</t>
+  </si>
+  <si>
+    <t>134546015</t>
+  </si>
+  <si>
+    <t>134597589</t>
+  </si>
+  <si>
+    <t>134598388</t>
+  </si>
+  <si>
+    <t>134451057</t>
+  </si>
+  <si>
+    <t>134456049</t>
   </si>
 </sst>
 </file>
@@ -474,7 +480,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -623,6 +629,40 @@
         <v>6</v>
       </c>
     </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3108F884-8791-439E-89C2-323F29A63FC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57FEF7BE-5D3A-49BB-ABCD-4788EDF7C267}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -54,37 +54,37 @@
     <t>971</t>
   </si>
   <si>
-    <t>Recusa Sicoob 23.09.2025</t>
-  </si>
-  <si>
-    <t>134454849</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 23.09.2025</t>
-  </si>
-  <si>
-    <t>134495213</t>
-  </si>
-  <si>
-    <t>134563149</t>
-  </si>
-  <si>
-    <t>130906283</t>
-  </si>
-  <si>
-    <t>134546015</t>
-  </si>
-  <si>
-    <t>134597589</t>
-  </si>
-  <si>
-    <t>134598388</t>
-  </si>
-  <si>
-    <t>134451057</t>
-  </si>
-  <si>
-    <t>134456049</t>
+    <t>Recusa Sicoob 24.09.2025</t>
+  </si>
+  <si>
+    <t>134501661</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 24.09.2025</t>
+  </si>
+  <si>
+    <t>134549137</t>
+  </si>
+  <si>
+    <t>134590814</t>
+  </si>
+  <si>
+    <t>134555606</t>
+  </si>
+  <si>
+    <t>134473702</t>
+  </si>
+  <si>
+    <t>134480576</t>
+  </si>
+  <si>
+    <t>134427697</t>
+  </si>
+  <si>
+    <t>134619358</t>
+  </si>
+  <si>
+    <t>134515530</t>
   </si>
 </sst>
 </file>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57FEF7BE-5D3A-49BB-ABCD-4788EDF7C267}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A4CDE93-D666-41DF-B512-3D6C2723C1EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -54,37 +54,37 @@
     <t>971</t>
   </si>
   <si>
-    <t>Recusa Sicoob 24.09.2025</t>
-  </si>
-  <si>
-    <t>134501661</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 24.09.2025</t>
-  </si>
-  <si>
-    <t>134549137</t>
-  </si>
-  <si>
-    <t>134590814</t>
-  </si>
-  <si>
-    <t>134555606</t>
-  </si>
-  <si>
-    <t>134473702</t>
-  </si>
-  <si>
-    <t>134480576</t>
-  </si>
-  <si>
-    <t>134427697</t>
-  </si>
-  <si>
-    <t>134619358</t>
-  </si>
-  <si>
-    <t>134515530</t>
+    <t>134652905</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 06.10.2025</t>
+  </si>
+  <si>
+    <t>134757779</t>
+  </si>
+  <si>
+    <t>134793399</t>
+  </si>
+  <si>
+    <t>134594937</t>
+  </si>
+  <si>
+    <t>134618493</t>
+  </si>
+  <si>
+    <t>134802339</t>
+  </si>
+  <si>
+    <t>134655357</t>
+  </si>
+  <si>
+    <t>134668223</t>
+  </si>
+  <si>
+    <t>134669848</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 06.10.2025</t>
   </si>
 </sst>
 </file>
@@ -512,16 +512,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -529,16 +529,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -546,16 +546,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -563,16 +563,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -580,16 +580,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -597,16 +597,16 @@
     </row>
     <row r="7" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -614,16 +614,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -631,16 +631,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -648,16 +648,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -677,31 +677,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A4CDE93-D666-41DF-B512-3D6C2723C1EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68F56199-D8FD-4F4A-86F8-0A637A190317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -677,31 +677,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68F56199-D8FD-4F4A-86F8-0A637A190317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15E9A800-2559-445F-8647-9B9278E8AB3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="15">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,37 +54,25 @@
     <t>971</t>
   </si>
   <si>
-    <t>134652905</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 06.10.2025</t>
-  </si>
-  <si>
-    <t>134757779</t>
-  </si>
-  <si>
-    <t>134793399</t>
-  </si>
-  <si>
-    <t>134594937</t>
-  </si>
-  <si>
-    <t>134618493</t>
-  </si>
-  <si>
-    <t>134802339</t>
-  </si>
-  <si>
-    <t>134655357</t>
-  </si>
-  <si>
-    <t>134668223</t>
-  </si>
-  <si>
-    <t>134669848</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 06.10.2025</t>
+    <t>134613594</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 08.10.2025</t>
+  </si>
+  <si>
+    <t>134714626</t>
+  </si>
+  <si>
+    <t>134703555</t>
+  </si>
+  <si>
+    <t>134818983</t>
+  </si>
+  <si>
+    <t>134710776</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 08.10.2025</t>
   </si>
 </sst>
 </file>
@@ -480,7 +468,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -521,7 +509,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -538,7 +526,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -555,7 +543,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -572,7 +560,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -589,80 +577,13 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
+    <row r="7" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -677,31 +598,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15E9A800-2559-445F-8647-9B9278E8AB3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CE9C68B-F8E1-4CAB-BCAA-606B29C88B15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="17">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,25 +54,31 @@
     <t>971</t>
   </si>
   <si>
-    <t>134613594</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 08.10.2025</t>
-  </si>
-  <si>
-    <t>134714626</t>
-  </si>
-  <si>
-    <t>134703555</t>
-  </si>
-  <si>
-    <t>134818983</t>
-  </si>
-  <si>
-    <t>134710776</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 08.10.2025</t>
+    <t>134852666</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 09.10.2025</t>
+  </si>
+  <si>
+    <t>134665426</t>
+  </si>
+  <si>
+    <t>134705963</t>
+  </si>
+  <si>
+    <t>134713834</t>
+  </si>
+  <si>
+    <t>134723821</t>
+  </si>
+  <si>
+    <t>132505320</t>
+  </si>
+  <si>
+    <t>134734905</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 09.10.2025</t>
   </si>
 </sst>
 </file>
@@ -468,7 +474,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -509,7 +515,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -526,7 +532,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -543,7 +549,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -560,7 +566,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -577,13 +583,46 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -598,31 +637,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CE9C68B-F8E1-4CAB-BCAA-606B29C88B15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEE8A73C-36D4-44FE-90E2-5E0618BC4202}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="22">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,31 +54,46 @@
     <t>971</t>
   </si>
   <si>
-    <t>134852666</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 09.10.2025</t>
-  </si>
-  <si>
-    <t>134665426</t>
-  </si>
-  <si>
-    <t>134705963</t>
-  </si>
-  <si>
-    <t>134713834</t>
-  </si>
-  <si>
-    <t>134723821</t>
-  </si>
-  <si>
-    <t>132505320</t>
-  </si>
-  <si>
-    <t>134734905</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 09.10.2025</t>
+    <t>Recusa Sicoob 10.10.2025</t>
+  </si>
+  <si>
+    <t>134758720</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 10.10.2025</t>
+  </si>
+  <si>
+    <t>134769703</t>
+  </si>
+  <si>
+    <t>134796381</t>
+  </si>
+  <si>
+    <t>131403608</t>
+  </si>
+  <si>
+    <t>134748304</t>
+  </si>
+  <si>
+    <t>134754290</t>
+  </si>
+  <si>
+    <t>134800887</t>
+  </si>
+  <si>
+    <t>134890662</t>
+  </si>
+  <si>
+    <t>134704375</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 11.10.2025</t>
+  </si>
+  <si>
+    <t>130154295</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 11.10.2025</t>
   </si>
 </sst>
 </file>
@@ -474,7 +489,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -506,16 +521,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -523,16 +538,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -540,16 +555,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -557,16 +572,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -574,16 +589,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -591,16 +606,16 @@
     </row>
     <row r="7" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -608,18 +623,86 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -637,31 +720,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEE8A73C-36D4-44FE-90E2-5E0618BC4202}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03B41BB1-09DA-4B95-AA4A-7CC107069915}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="21">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,46 +54,43 @@
     <t>971</t>
   </si>
   <si>
-    <t>Recusa Sicoob 10.10.2025</t>
-  </si>
-  <si>
-    <t>134758720</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 10.10.2025</t>
-  </si>
-  <si>
-    <t>134769703</t>
-  </si>
-  <si>
-    <t>134796381</t>
-  </si>
-  <si>
-    <t>131403608</t>
-  </si>
-  <si>
-    <t>134748304</t>
-  </si>
-  <si>
-    <t>134754290</t>
-  </si>
-  <si>
-    <t>134800887</t>
-  </si>
-  <si>
-    <t>134890662</t>
-  </si>
-  <si>
-    <t>134704375</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 11.10.2025</t>
-  </si>
-  <si>
-    <t>130154295</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 11.10.2025</t>
+    <t>130744852</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 13.10.2025</t>
+  </si>
+  <si>
+    <t>134782997</t>
+  </si>
+  <si>
+    <t>134766301</t>
+  </si>
+  <si>
+    <t>134804038</t>
+  </si>
+  <si>
+    <t>134847504</t>
+  </si>
+  <si>
+    <t>134821212</t>
+  </si>
+  <si>
+    <t>134876934</t>
+  </si>
+  <si>
+    <t>134860059</t>
+  </si>
+  <si>
+    <t>134711705</t>
+  </si>
+  <si>
+    <t>134766644</t>
+  </si>
+  <si>
+    <t>134779701</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 13.10.2025</t>
   </si>
 </sst>
 </file>
@@ -521,16 +518,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -538,16 +535,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -555,16 +552,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -572,16 +569,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -589,16 +586,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -606,16 +603,16 @@
     </row>
     <row r="7" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -623,16 +620,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -640,16 +637,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -657,16 +654,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -680,10 +677,10 @@
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -691,16 +688,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -720,31 +717,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03B41BB1-09DA-4B95-AA4A-7CC107069915}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA5955B3-2A14-493E-9DE6-A1DBDAAF3E4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="36">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,43 +54,88 @@
     <t>971</t>
   </si>
   <si>
-    <t>130744852</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 13.10.2025</t>
-  </si>
-  <si>
-    <t>134782997</t>
-  </si>
-  <si>
-    <t>134766301</t>
-  </si>
-  <si>
-    <t>134804038</t>
-  </si>
-  <si>
-    <t>134847504</t>
-  </si>
-  <si>
-    <t>134821212</t>
-  </si>
-  <si>
-    <t>134876934</t>
-  </si>
-  <si>
-    <t>134860059</t>
-  </si>
-  <si>
-    <t>134711705</t>
-  </si>
-  <si>
-    <t>134766644</t>
-  </si>
-  <si>
-    <t>134779701</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 13.10.2025</t>
+    <t>134782182</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 15.10.2025</t>
+  </si>
+  <si>
+    <t>134831057</t>
+  </si>
+  <si>
+    <t>134841462</t>
+  </si>
+  <si>
+    <t>134834773</t>
+  </si>
+  <si>
+    <t>134864537</t>
+  </si>
+  <si>
+    <t>134905353</t>
+  </si>
+  <si>
+    <t>134929813</t>
+  </si>
+  <si>
+    <t>134749381</t>
+  </si>
+  <si>
+    <t>134821669</t>
+  </si>
+  <si>
+    <t>134864152</t>
+  </si>
+  <si>
+    <t>134843513</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 15.10.2025</t>
+  </si>
+  <si>
+    <t>134877013</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 16.10.2025</t>
+  </si>
+  <si>
+    <t>134921807</t>
+  </si>
+  <si>
+    <t>134737649</t>
+  </si>
+  <si>
+    <t>134959332</t>
+  </si>
+  <si>
+    <t>134960092</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 16.10.2025</t>
+  </si>
+  <si>
+    <t>130523741</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 14.10.2025</t>
+  </si>
+  <si>
+    <t>134848767</t>
+  </si>
+  <si>
+    <t>134835389</t>
+  </si>
+  <si>
+    <t>134857780</t>
+  </si>
+  <si>
+    <t>134835495</t>
+  </si>
+  <si>
+    <t>134726993</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 14.10.2025</t>
   </si>
 </sst>
 </file>
@@ -486,7 +531,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -700,6 +745,193 @@
         <v>20</v>
       </c>
       <c r="E12" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -717,31 +949,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA5955B3-2A14-493E-9DE6-A1DBDAAF3E4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C410C17-412F-4739-880A-358BEC8EEDBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="14">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,95 +54,29 @@
     <t>971</t>
   </si>
   <si>
-    <t>134782182</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 15.10.2025</t>
-  </si>
-  <si>
-    <t>134831057</t>
-  </si>
-  <si>
-    <t>134841462</t>
-  </si>
-  <si>
-    <t>134834773</t>
-  </si>
-  <si>
-    <t>134864537</t>
-  </si>
-  <si>
-    <t>134905353</t>
-  </si>
-  <si>
-    <t>134929813</t>
-  </si>
-  <si>
-    <t>134749381</t>
-  </si>
-  <si>
-    <t>134821669</t>
-  </si>
-  <si>
-    <t>134864152</t>
-  </si>
-  <si>
-    <t>134843513</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 15.10.2025</t>
-  </si>
-  <si>
-    <t>134877013</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 16.10.2025</t>
-  </si>
-  <si>
-    <t>134921807</t>
-  </si>
-  <si>
-    <t>134737649</t>
-  </si>
-  <si>
-    <t>134959332</t>
-  </si>
-  <si>
-    <t>134960092</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 16.10.2025</t>
-  </si>
-  <si>
-    <t>130523741</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 14.10.2025</t>
-  </si>
-  <si>
-    <t>134848767</t>
-  </si>
-  <si>
-    <t>134835389</t>
-  </si>
-  <si>
-    <t>134857780</t>
-  </si>
-  <si>
-    <t>134835495</t>
-  </si>
-  <si>
-    <t>134726993</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 14.10.2025</t>
+    <t>Relatório de Recusa SICOOB 17.10.2025</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 17.10.2025</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 18.10.2025</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 18.10.2025</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 20.10.2025</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 20.10.2025</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -163,6 +97,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -185,7 +125,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -193,11 +133,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -212,13 +167,74 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -531,7 +547,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -562,382 +578,241 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>9</v>
+      <c r="A2" s="6">
+        <v>134825896</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="6">
+        <v>134873846</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="6">
+        <v>134847875</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="6">
+        <v>134903585</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="6">
+        <v>134825442</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="6">
+        <v>131153815</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="6">
+        <v>134984381</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="6">
+        <v>134804640</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="6">
+        <v>134990602</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="6">
+        <v>134861452</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="9">
+        <v>134954227</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="D12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="E12" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="9">
+        <v>133754841</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="10">
+        <v>134847793</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="D14" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="E14" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E23" s="2" t="s">
         <v>6</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
+  <conditionalFormatting sqref="A2:A11">
+    <cfRule type="duplicateValues" dxfId="5" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A12:A13">
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A14">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
@@ -949,31 +824,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C410C17-412F-4739-880A-358BEC8EEDBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A502220C-302D-47DE-BCFC-C8D94427A262}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="10">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,22 +54,10 @@
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa SICOOB 17.10.2025</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 17.10.2025</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 18.10.2025</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 18.10.2025</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 20.10.2025</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 20.10.2025</t>
+    <t>Relatório de Recusa SICOOB 21.10.2025</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 21.10.2025</t>
   </si>
 </sst>
 </file>
@@ -579,7 +567,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>134825896</v>
+        <v>134886432</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>7</v>
@@ -596,7 +584,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
-        <v>134873846</v>
+        <v>134879493</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>7</v>
@@ -613,7 +601,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
-        <v>134847875</v>
+        <v>134885672</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>7</v>
@@ -630,7 +618,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
-        <v>134903585</v>
+        <v>134949059</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>7</v>
@@ -647,7 +635,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
-        <v>134825442</v>
+        <v>130741861</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>7</v>
@@ -664,7 +652,7 @@
     </row>
     <row r="7" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
-        <v>131153815</v>
+        <v>130623019</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>7</v>
@@ -681,7 +669,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
-        <v>134984381</v>
+        <v>134846084</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>7</v>
@@ -698,7 +686,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
-        <v>134804640</v>
+        <v>131496901</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>7</v>
@@ -715,7 +703,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
-        <v>134990602</v>
+        <v>135032959</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>7</v>
@@ -732,7 +720,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
-        <v>134861452</v>
+        <v>134891043</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>7</v>
@@ -749,54 +737,30 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="9">
-        <v>134954227</v>
+        <v>134967188</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="9">
-        <v>133754841</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="A13" s="9"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="8"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="10">
-        <v>134847793</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="A14" s="10"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="8"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -824,31 +788,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A502220C-302D-47DE-BCFC-C8D94427A262}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5368CBC2-99B6-4DAD-972D-93EA7FE3BC87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="10">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,10 +54,10 @@
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa SICOOB 21.10.2025</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 21.10.2025</t>
+    <t>Relatório de Recusa SICOOB 22.10.2025</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 22.10.2025</t>
   </si>
 </sst>
 </file>
@@ -567,7 +567,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>134886432</v>
+        <v>134965721</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>7</v>
@@ -584,7 +584,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
-        <v>134879493</v>
+        <v>135043185</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>7</v>
@@ -601,7 +601,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
-        <v>134885672</v>
+        <v>134950498</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>7</v>
@@ -618,7 +618,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
-        <v>134949059</v>
+        <v>134866889</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>7</v>
@@ -634,123 +634,39 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
-        <v>130741861</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="A6" s="6"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="8"/>
     </row>
     <row r="7" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
-        <v>130623019</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="A7" s="6"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="8"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
-        <v>134846084</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="A8" s="6"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="6">
-        <v>131496901</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="A9" s="6"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="8"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="6">
-        <v>135032959</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="A10" s="6"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="8"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="6">
-        <v>134891043</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="A11" s="6"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="8"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="9">
-        <v>134967188</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="A12" s="9"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="8"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="9"/>
@@ -788,31 +704,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5368CBC2-99B6-4DAD-972D-93EA7FE3BC87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF2A1DAB-8B52-44D1-9BFA-C73A65A5EC19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="11">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -57,7 +57,10 @@
     <t>Relatório de Recusa SICOOB 22.10.2025</t>
   </si>
   <si>
-    <t>Recusa Sicoob 22.10.2025</t>
+    <t>Relatório de Recusa SICOOB 23.10.2025</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 23.10.2025</t>
   </si>
 </sst>
 </file>
@@ -576,7 +579,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -584,16 +587,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
-        <v>135043185</v>
+        <v>134997409</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -601,16 +604,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
-        <v>134950498</v>
+        <v>135026635</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -618,35 +621,71 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
-        <v>134866889</v>
+        <v>134994690</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="6"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="8"/>
+      <c r="A6" s="6">
+        <v>130907521</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="7" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="6"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="8"/>
+      <c r="A7" s="6">
+        <v>135029106</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="6"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="8"/>
+      <c r="A8" s="6">
+        <v>134953032</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="6"/>
@@ -704,31 +743,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF2A1DAB-8B52-44D1-9BFA-C73A65A5EC19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F08D4A02-0E5F-455A-ABEF-A9C9D4472749}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="10">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,13 +54,10 @@
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa SICOOB 22.10.2025</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 23.10.2025</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 23.10.2025</t>
+    <t>Recusa Sicoob 24.10.2025</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 24.10.2025</t>
   </si>
 </sst>
 </file>
@@ -570,16 +567,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>134965721</v>
+        <v>134875044</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -587,7 +584,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
-        <v>134997409</v>
+        <v>135074734</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>7</v>
@@ -596,7 +593,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -604,7 +601,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
-        <v>135026635</v>
+        <v>134980797</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>7</v>
@@ -613,7 +610,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -621,7 +618,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
-        <v>134994690</v>
+        <v>134968908</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>7</v>
@@ -630,7 +627,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -638,7 +635,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
-        <v>130907521</v>
+        <v>134974393</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>7</v>
@@ -647,7 +644,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -655,7 +652,7 @@
     </row>
     <row r="7" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
-        <v>135029106</v>
+        <v>133425615</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>7</v>
@@ -664,28 +661,16 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
-        <v>134953032</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="A8" s="6"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="6"/>
@@ -743,31 +728,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F08D4A02-0E5F-455A-ABEF-A9C9D4472749}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49ACDE6E-E716-46EE-9905-DE3D4AE1D821}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="10">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -57,7 +57,7 @@
     <t>Recusa Sicoob 24.10.2025</t>
   </si>
   <si>
-    <t>Relatório de Recusa SICOOB 24.10.2025</t>
+    <t>Relatório de Recusa SICOOB 27.10.2025</t>
   </si>
 </sst>
 </file>
@@ -567,7 +567,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>134875044</v>
+        <v>135064587</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>7</v>
@@ -584,7 +584,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
-        <v>135074734</v>
+        <v>134924586</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>7</v>
@@ -601,7 +601,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
-        <v>134980797</v>
+        <v>134948391</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>7</v>
@@ -617,55 +617,19 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
-        <v>134968908</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="A5" s="6"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="8"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
-        <v>134974393</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="A6" s="6"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="8"/>
     </row>
     <row r="7" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
-        <v>133425615</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="A7" s="6"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="8"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="6"/>
@@ -728,31 +692,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49ACDE6E-E716-46EE-9905-DE3D4AE1D821}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC4D499A-1B86-43FC-B552-B6195F137374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -140,7 +140,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -165,48 +165,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <font>
         <color rgb="FF00B050"/>
@@ -535,7 +499,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -616,70 +580,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="6"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="8"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="6"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="8"/>
-    </row>
-    <row r="7" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="6"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="8"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="6"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="8"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="6"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="8"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="6"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="8"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="6"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="8"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="9"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="8"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="9"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="8"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="10"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="8"/>
-    </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="A2:A11">
-    <cfRule type="duplicateValues" dxfId="5" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A12:A13">
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A14">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  <conditionalFormatting sqref="A2:A4">
+    <cfRule type="duplicateValues" dxfId="1" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
   </conditionalFormatting>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -692,31 +598,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B50686E-51A6-41C0-BEEC-91C30B46B4ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40EF2C5F-C522-4550-92D2-9168E7F1F102}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="14">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,70 +54,22 @@
     <t>971</t>
   </si>
   <si>
-    <t>134657698</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 03.10.2025</t>
-  </si>
-  <si>
-    <t>134687820</t>
-  </si>
-  <si>
-    <t>134731327</t>
-  </si>
-  <si>
-    <t>134684491</t>
-  </si>
-  <si>
-    <t>134667439</t>
-  </si>
-  <si>
-    <t>134578392</t>
-  </si>
-  <si>
-    <t>134666153</t>
-  </si>
-  <si>
-    <t>134572998</t>
-  </si>
-  <si>
-    <t>134646332</t>
-  </si>
-  <si>
-    <t>134769808</t>
-  </si>
-  <si>
-    <t>132505320</t>
-  </si>
-  <si>
-    <t>134775661</t>
-  </si>
-  <si>
-    <t>133713907</t>
-  </si>
-  <si>
-    <t>134584773</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 04.10.2025</t>
-  </si>
-  <si>
-    <t>134660132</t>
-  </si>
-  <si>
-    <t>134707319</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 05.10.2025</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 03.10.2025</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 04.10.2025</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 05.10.2025</t>
+    <t>135743548</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 18.12.2025</t>
+  </si>
+  <si>
+    <t>135829472</t>
+  </si>
+  <si>
+    <t>135833541</t>
+  </si>
+  <si>
+    <t>135913899</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 18.12.2025</t>
   </si>
 </sst>
 </file>
@@ -513,7 +465,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -554,11 +506,12 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -571,11 +524,12 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -588,11 +542,12 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
@@ -605,215 +560,12 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="F5"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -829,31 +581,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40EF2C5F-C522-4550-92D2-9168E7F1F102}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr documentId="13_ncr:1_{EF97C44E-9395-4774-ADA8-D810911623CE}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="11040" windowWidth="20730" xWindow="-120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" yWindow="-120"/>
   </bookViews>
   <sheets>
-    <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
+    <sheet name="IndexacaoFG" r:id="rId1" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">IndexacaoFG!$A$1:$F$1</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">IndexacaoFG!$A$1:$F$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,29 +54,24 @@
     <t>971</t>
   </si>
   <si>
-    <t>135743548</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 18.12.2025</t>
-  </si>
-  <si>
-    <t>135829472</t>
-  </si>
-  <si>
-    <t>135833541</t>
-  </si>
-  <si>
-    <t>135913899</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 18.12.2025</t>
+    <t>Relatório de Recusa SICOOB 01.10.2026</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 01.10.2026</t>
+  </si>
+  <si>
+    <t>Processado</t>
+  </si>
+  <si>
+    <t>&lt;u&gt;Documentos indexados&lt;/u&gt;:1-&gt; Recusa Sicoob 01.10.2026.xlsx.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -97,6 +92,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -119,7 +120,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -127,33 +128,68 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+  <cellXfs count="9">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
+    <xf applyAlignment="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="49" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="0" fillId="2" fontId="1" numFmtId="49" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf applyAlignment="1" applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf applyAlignment="1" applyFill="1" applyFont="1" borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf applyAlignment="1" applyBorder="1" borderId="1" fillId="0" fontId="0" numFmtId="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle builtinId="0" name="Normal" xfId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -170,10 +206,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -208,7 +244,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -260,7 +296,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -371,21 +407,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -402,7 +438,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -454,25 +490,25 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="4" width="49.5703125" style="2" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="16.42578125" style="2" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="84.7109375" style="2" customWidth="1" collapsed="1"/>
-    <col min="7" max="16384" width="9.140625" style="2" collapsed="1"/>
+    <col min="1" max="2" customWidth="true" style="1" width="16.7109375" collapsed="true"/>
+    <col min="3" max="4" customWidth="true" style="2" width="49.5703125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="2" width="16.42578125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="2" width="84.7109375" collapsed="true"/>
+    <col min="7" max="16384" style="2" width="9.140625" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -496,116 +532,67 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="6">
+        <v>141006670</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="E2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="F2" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <conditionalFormatting sqref="A2">
+    <cfRule dxfId="0" priority="3" type="duplicateValues"/>
+  </conditionalFormatting>
+  <pageMargins bottom="0.78740157480314965" footer="0.31496062992125984" header="0.31496062992125984" left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965"/>
+  <pageSetup orientation="portrait" paperSize="9" r:id="rId1"/>
   <headerFooter>
-    <oddFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FINTERNO</oddFooter>
-    <evenFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FINTERNO</evenFooter>
-    <firstFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FINTERNO</firstFooter>
+    <oddFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FINTERNO]]></oddFooter>
+    <evenFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FINTERNO]]></evenFooter>
+    <firstFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FINTERNO]]></firstFooter>
   </headerFooter>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>